--- a/XLibur.Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
@@ -20,10 +20,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>Avg:</x:t>
+    <x:t>Sum:</x:t>
   </x:si>
   <x:si>
-    <x:t>Sum:</x:t>
+    <x:t>Avg:</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -411,7 +411,7 @@
         <x:f>SUM(C3:D3)</x:f>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G3" s="0">
         <x:f>Average(C3:D4)</x:f>
@@ -430,7 +430,7 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="B5" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:f>Sum(C3:C4)</x:f>

--- a/XLibur.Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
@@ -391,40 +391,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:G5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="2" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="1" max="2" width="9.140625"/>
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="1:7">
-      <x:c r="C3" s="0">
+      <x:c r="C3">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D3" s="0">
+      <x:c r="D3">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E3" s="0">
+      <x:c r="E3">
         <x:f>SUM(C3:D3)</x:f>
       </x:c>
       <x:c r="F3" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G3" s="0">
+      <x:c r="G3">
         <x:f>Average(C3:D4)</x:f>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
-      <x:c r="C4" s="0">
+      <x:c r="C4">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D4" s="0">
+      <x:c r="D4">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E4" s="0">
+      <x:c r="E4">
         <x:f>SUM(C4:D4)</x:f>
       </x:c>
     </x:row>
@@ -432,83 +429,72 @@
       <x:c r="B5" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C5" s="0">
+      <x:c r="C5">
         <x:f>Sum(C3:C4)</x:f>
       </x:c>
-      <x:c r="D5" s="0">
+      <x:c r="D5">
         <x:f>Sum(D3:D4)</x:f>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:B9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:2">
-      <x:c r="A1" s="0">
+      <x:c r="A1">
         <x:f>'Shifting Formulas'!C3</x:f>
       </x:c>
-      <x:c r="B1" s="0">
+      <x:c r="B1">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
-      <x:c r="A2" s="0">
+      <x:c r="A2">
         <x:f>Average('Shifting Formulas'!$C$3:$D$4)</x:f>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
-      <x:c r="A3" s="0">
+      <x:c r="A3">
         <x:f>Average('Shifting Formulas'!$C$3:$D4)</x:f>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
-      <x:c r="A4" s="0">
+      <x:c r="A4">
         <x:f>Average('Shifting Formulas'!$C$3:D4)</x:f>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
-      <x:c r="A5" s="0">
+      <x:c r="A5">
         <x:f>Average('Shifting Formulas'!$C3:D4)</x:f>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
-      <x:c r="A6" s="0">
+      <x:c r="A6">
         <x:f>Average('Shifting Formulas'!C3:D4)</x:f>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
-      <x:c r="A7" s="0">
+      <x:c r="A7">
         <x:f>Average('Shifting Formulas'!C3:D$4)</x:f>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
-      <x:c r="A8" s="0">
+      <x:c r="A8">
         <x:f>Average('Shifting Formulas'!C3:$D$4)</x:f>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
-      <x:c r="A9" s="0">
+      <x:c r="A9">
         <x:f>Average('Shifting Formulas'!C$3:$D$4)</x:f>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
@@ -394,7 +394,7 @@
   <x:dimension ref="A1:G5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="2" width="9.140625"/>
+    <x:col min="1" max="2" width="9.144286"/>
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="1:7">
